--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536318_LIGAREGULARB_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536318_LIGAREGULARB_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,7 +712,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -724,67 +724,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8753</v>
+        <v>-0.1005</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8753</v>
+        <v>-0.2551</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.1546</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8753</v>
+        <v>-0.5093</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8753</v>
+        <v>-2.2211</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1.7118</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8753</v>
+        <v>0.6113</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8753</v>
+        <v>-1.3219</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.9331</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1.1206</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.8992</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.2214</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.2329</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.2603</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.354</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.1611</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.1929</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.1781</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.1781</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>G. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -807,67 +807,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1005</v>
+        <v>-0.2279</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2551</v>
+        <v>0.6273</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1546</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5093</v>
+        <v>0.0373</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.2211</v>
+        <v>0.7852</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7118</v>
+        <v>-0.7479</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6113</v>
+        <v>2.0746</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3219</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9331</v>
+        <v>1.3837</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1206</v>
+        <v>-2.0373</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8992</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2214</v>
+        <v>-2.1315</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2329</v>
+        <v>1.0274</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0274</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2603</v>
+        <v>2.0548</v>
       </c>
       <c r="S5" t="n">
-        <v>0.354</v>
+        <v>-0.5858</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1611</v>
+        <v>-0.4199</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1929</v>
+        <v>-0.1659</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1781</v>
+        <v>-0.7068</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1781</v>
+        <v>-0.7068</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. IGLESIAS FERNANDEZ</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,67 +890,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2279</v>
+        <v>-0.2823</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6273</v>
+        <v>-0.3372</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8552999999999999</v>
+        <v>0.0549</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0373</v>
+        <v>0.0611</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7852</v>
+        <v>3.7361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7479</v>
+        <v>-3.675</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0746</v>
+        <v>1.9352</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6909999999999999</v>
+        <v>3.5893</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3837</v>
+        <v>-1.6541</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0373</v>
+        <v>-1.874</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.1315</v>
+        <v>-2.0208</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0274</v>
+        <v>0.2055</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0274</v>
+        <v>-2.0548</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0548</v>
+        <v>2.2603</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5858</v>
+        <v>-0.3215</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4199</v>
+        <v>-0.108</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1659</v>
+        <v>-0.2135</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7068</v>
+        <v>-0.2274</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.1096</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7068</v>
+        <v>-0.1178</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CEBOLLA PORCAR</t>
+          <t>K. BAOKO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,67 +973,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2823</v>
+        <v>-0.4668</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3372</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0549</v>
+        <v>-0.5654</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0611</v>
+        <v>-0.5817</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7361</v>
+        <v>0.2003</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.675</v>
+        <v>-0.7819</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9352</v>
+        <v>0.9762</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5893</v>
+        <v>0.7789</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.6541</v>
+        <v>0.1973</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.874</v>
+        <v>-1.5579</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1468</v>
+        <v>-0.5787</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.0208</v>
+        <v>-0.9792</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2055</v>
+        <v>1.8493</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0548</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2603</v>
+        <v>1.8493</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3215</v>
+        <v>-0.3289</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.108</v>
+        <v>-0.1789</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2135</v>
+        <v>-0.15</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2274</v>
+        <v>-1.4055</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1096</v>
+        <v>-0.6986</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1178</v>
+        <v>-0.7068</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. BAOKO</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,67 +1056,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4668</v>
+        <v>-1.3072</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09859999999999999</v>
+        <v>-2.6552</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5654</v>
+        <v>1.348</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5817</v>
+        <v>-3.3871</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2003</v>
+        <v>-2.157</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7819</v>
+        <v>-1.2301</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9762</v>
+        <v>-2.661</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7789</v>
+        <v>-1.3997</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1973</v>
+        <v>-1.2613</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5579</v>
+        <v>-0.7261</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5787</v>
+        <v>-0.7573</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9792</v>
+        <v>0.0312</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8493</v>
+        <v>0.8219</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R8" t="n">
         <v>1.8493</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3289</v>
+        <v>0.0798</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1789</v>
+        <v>-0.1449</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.15</v>
+        <v>0.2247</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4055</v>
+        <v>1.1781</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6986</v>
+        <v>1.1781</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7068</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. MULERO MALDONADO</t>
+          <t>D. LOZANO GIMENEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3072</v>
+        <v>-1.5434</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6552</v>
+        <v>-0.647</v>
       </c>
       <c r="F9" t="n">
-        <v>1.348</v>
+        <v>-0.8964</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3871</v>
+        <v>-1.0553</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.157</v>
+        <v>-0.5584</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2301</v>
+        <v>-0.497</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.661</v>
+        <v>-0.5923</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3997</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2613</v>
+        <v>-0.6701</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7261</v>
+        <v>-0.463</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7573</v>
+        <v>-0.6362</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0312</v>
+        <v>0.1731</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8219</v>
+        <v>1.0274</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0274</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8493</v>
+        <v>1.0274</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0798</v>
+        <v>-0.3374</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1449</v>
+        <v>-0.0547</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2247</v>
+        <v>-0.2827</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1781</v>
+        <v>-1.1781</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1781</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1781</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. LOZANO GIMENEZ</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,58 +1222,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5434</v>
+        <v>-2.1928</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.647</v>
+        <v>-1.2969</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8964</v>
+        <v>-0.8959</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0553</v>
+        <v>-0.583</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5584</v>
+        <v>0.4509</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.497</v>
+        <v>-1.034</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5923</v>
+        <v>0.1962</v>
       </c>
       <c r="K10" t="n">
         <v>0.07779999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6701</v>
+        <v>0.1184</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.463</v>
+        <v>-0.7792</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6362</v>
+        <v>0.3731</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1731</v>
+        <v>-1.1523</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0274</v>
+        <v>-0.2055</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0274</v>
+        <v>0.8219</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3374</v>
+        <v>-0.2262</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0547</v>
+        <v>-0.4657</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2827</v>
+        <v>0.2395</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1781</v>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>R. DIAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1928</v>
+        <v>-5.8268</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2969</v>
+        <v>-4.0997</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8959</v>
+        <v>-1.7271</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.583</v>
+        <v>-2.6098</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4509</v>
+        <v>0.6636</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.034</v>
+        <v>-3.2734</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1962</v>
+        <v>-1.5621</v>
       </c>
       <c r="K11" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.4483</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1184</v>
+        <v>-2.0103</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7792</v>
+        <v>-1.0477</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3731</v>
+        <v>0.2153</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1523</v>
+        <v>-1.263</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2055</v>
+        <v>-1.2329</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0274</v>
+        <v>-2.0548</v>
       </c>
       <c r="R11" t="n">
         <v>0.8219</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2262</v>
+        <v>0.5994</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4657</v>
+        <v>0.2158</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2395</v>
+        <v>0.3836</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1781</v>
+        <v>-2.5836</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.6986</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1781</v>
+        <v>-1.8849</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. DIAZ DEL VALLE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1471,157 +1471,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.7021</v>
+        <v>-14.9273</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9751</v>
+        <v>-13.5049</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7271</v>
+        <v>-1.4225</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.4851</v>
+        <v>-14.1421</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2118</v>
+        <v>-1.6823</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.2734</v>
+        <v>-12.46</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.4374</v>
+        <v>1.647699999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4271</v>
+        <v>2.3428</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.0103</v>
+        <v>-0.6951000000000007</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0477</v>
+        <v>-15.7896</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2153</v>
+        <v>-4.025099999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.263</v>
+        <v>-11.7645</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.2329</v>
+        <v>7.191800000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0548</v>
+        <v>-14.3836</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8219</v>
+        <v>21.5755</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5994</v>
+        <v>-0.3402000000000003</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2158</v>
+        <v>-1.5084</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3836</v>
+        <v>1.1683</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.5836</v>
+        <v>-7.637</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.6986</v>
+        <v>0.7396999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.8849</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>play_by_play_2536318_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-8.3766</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMICS CASTELLÓ</t>
+          <t>CLASS BASQUET SANT ANTONI</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.9273</v>
+        <v>7.0856</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.505</v>
+        <v>6.4268</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4225</v>
+        <v>0.6587</v>
       </c>
       <c r="G14" t="n">
-        <v>-14.1421</v>
+        <v>7.9426</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.6824</v>
+        <v>4.0769</v>
       </c>
       <c r="I14" t="n">
-        <v>-12.46</v>
+        <v>3.8657</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6477</v>
+        <v>8.2288</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3427</v>
+        <v>3.4151</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6951000000000003</v>
+        <v>4.8137</v>
       </c>
       <c r="M14" t="n">
-        <v>-15.7896</v>
+        <v>-0.2861</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.0251</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-11.7645</v>
+        <v>-0.948</v>
       </c>
       <c r="P14" t="n">
-        <v>7.1918</v>
+        <v>-1.0274</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.3836</v>
+        <v>-3.2877</v>
       </c>
       <c r="R14" t="n">
-        <v>21.5755</v>
+        <v>2.2603</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3402000000000001</v>
+        <v>0.5196</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5084</v>
+        <v>0.0679</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1683</v>
+        <v>0.4517</v>
       </c>
       <c r="V14" t="n">
-        <v>-7.636999999999999</v>
+        <v>-0.3493</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7396999999999999</v>
+        <v>1.4178</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.3766</v>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+        <v>-1.7671</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2536318_LIGAREGULARB_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,67 +1633,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.0856</v>
+        <v>3.4266</v>
       </c>
       <c r="E15" t="n">
-        <v>6.4268</v>
+        <v>3.8986</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6587</v>
+        <v>-0.4719</v>
       </c>
       <c r="G15" t="n">
-        <v>7.9426</v>
+        <v>2.6049</v>
       </c>
       <c r="H15" t="n">
-        <v>4.0769</v>
+        <v>-1.3709</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8657</v>
+        <v>3.9758</v>
       </c>
       <c r="J15" t="n">
-        <v>8.2288</v>
+        <v>4.1573</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4151</v>
+        <v>0.4483</v>
       </c>
       <c r="L15" t="n">
-        <v>4.8137</v>
+        <v>3.709</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2861</v>
+        <v>-1.5524</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6618000000000001</v>
+        <v>-1.8192</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.948</v>
+        <v>0.2668</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.0274</v>
+        <v>0.411</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.2877</v>
+        <v>-0.2055</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2603</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5196</v>
+        <v>0.6505</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0679</v>
+        <v>-0.0533</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4517</v>
+        <v>0.7037</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3493</v>
+        <v>-0.2397</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4178</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7671</v>
+        <v>-0.2397</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>I. RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4266</v>
+        <v>2.9237</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8986</v>
+        <v>-0.061</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4719</v>
+        <v>2.9848</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6049</v>
+        <v>0.3066</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3709</v>
+        <v>-1.5071</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9758</v>
+        <v>1.8136</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1573</v>
+        <v>-0.107</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4483</v>
+        <v>-1.3701</v>
       </c>
       <c r="L16" t="n">
-        <v>3.709</v>
+        <v>1.263</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5524</v>
+        <v>0.4136</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8192</v>
+        <v>-0.137</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2668</v>
+        <v>0.5506</v>
       </c>
       <c r="P16" t="n">
-        <v>0.411</v>
+        <v>1.0274</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2055</v>
+        <v>-1.0274</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6163999999999999</v>
+        <v>2.0548</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6505</v>
+        <v>1.3501</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0533</v>
+        <v>0.8337</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7037</v>
+        <v>0.5164</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2397</v>
+        <v>0.2397</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2397</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2397</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. RUIZ GONZALEZ</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9237</v>
+        <v>2.8</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.061</v>
+        <v>0.6736</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9848</v>
+        <v>2.1264</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3066</v>
+        <v>0.4235</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5071</v>
+        <v>0.0619</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8136</v>
+        <v>0.3616</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.107</v>
+        <v>0.5775</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3701</v>
+        <v>0.3408</v>
       </c>
       <c r="L17" t="n">
-        <v>1.263</v>
+        <v>0.2367</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4136</v>
+        <v>-0.1541</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.137</v>
+        <v>-0.2789</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5506</v>
+        <v>0.1249</v>
       </c>
       <c r="P17" t="n">
-        <v>1.0274</v>
+        <v>2.2603</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0274</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0548</v>
+        <v>2.2603</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3501</v>
+        <v>0.3559</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8337</v>
+        <v>0.096</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5164</v>
+        <v>0.2599</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2397</v>
+        <v>-0.2397</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2397</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2397</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>G. GANTT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8</v>
+        <v>2.213</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6736</v>
+        <v>1.1116</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1264</v>
+        <v>1.1014</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4235</v>
+        <v>0.2323</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0619</v>
+        <v>-1.1167</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3616</v>
+        <v>1.349</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5775</v>
+        <v>0.5442</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3408</v>
+        <v>0.0296</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2367</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1541</v>
+        <v>-0.3119</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2789</v>
+        <v>-1.1463</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1249</v>
+        <v>0.8344</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2603</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2603</v>
+        <v>1.0274</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3559</v>
+        <v>-0.3755</v>
       </c>
       <c r="T18" t="n">
-        <v>0.096</v>
+        <v>-0.7614</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2599</v>
+        <v>0.3859</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2397</v>
+        <v>2.3561</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.3561</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2397</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. GANTT</t>
+          <t>D. DE LA RUA DE AGUSTIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.213</v>
+        <v>1.1201</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1116</v>
+        <v>-2.8041</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1014</v>
+        <v>3.9242</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2323</v>
+        <v>1.34</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1167</v>
+        <v>-1.6402</v>
       </c>
       <c r="I19" t="n">
-        <v>1.349</v>
+        <v>2.9802</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5442</v>
+        <v>0.5746</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0296</v>
+        <v>-1.398</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5145999999999999</v>
+        <v>1.9726</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3119</v>
+        <v>0.7653</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1463</v>
+        <v>-0.2422</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8344</v>
+        <v>1.0076</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-4.3151</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0274</v>
+        <v>-6.1644</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0274</v>
+        <v>1.8493</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3755</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7614</v>
+        <v>-0.3992</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3859</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>2.3561</v>
+        <v>3.5342</v>
       </c>
       <c r="W19" t="n">
-        <v>2.3561</v>
+        <v>3.1849</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3493</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. DE LA RUA DE AGUSTIN</t>
+          <t>M. STILMA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1201</v>
+        <v>0.87</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8041</v>
+        <v>-1.8044</v>
       </c>
       <c r="F20" t="n">
-        <v>3.9242</v>
+        <v>2.6744</v>
       </c>
       <c r="G20" t="n">
-        <v>1.34</v>
+        <v>2.7265</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6402</v>
+        <v>4.115</v>
       </c>
       <c r="I20" t="n">
-        <v>2.9802</v>
+        <v>-1.3885</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5746</v>
+        <v>2.7814</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.398</v>
+        <v>3.6477</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9726</v>
+        <v>-0.8662</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7653</v>
+        <v>-0.0549</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2422</v>
+        <v>0.4673</v>
       </c>
       <c r="O20" t="n">
-        <v>1.0076</v>
+        <v>-0.5222</v>
       </c>
       <c r="P20" t="n">
-        <v>-4.3151</v>
+        <v>-3.4932</v>
       </c>
       <c r="Q20" t="n">
-        <v>-6.1644</v>
+        <v>-5.3425</v>
       </c>
       <c r="R20" t="n">
         <v>1.8493</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5610000000000001</v>
+        <v>-0.0003</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3992</v>
+        <v>-0.4214</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.421</v>
       </c>
       <c r="V20" t="n">
-        <v>3.5342</v>
+        <v>1.637</v>
       </c>
       <c r="W20" t="n">
-        <v>3.1849</v>
+        <v>1.1781</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3493</v>
+        <v>0.4589</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. STILMA</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.87</v>
+        <v>-0.0105</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8044</v>
+        <v>-2.1043</v>
       </c>
       <c r="F21" t="n">
-        <v>2.6744</v>
+        <v>2.0937</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7265</v>
+        <v>-0.4973</v>
       </c>
       <c r="H21" t="n">
-        <v>4.115</v>
+        <v>0.7016</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3885</v>
+        <v>-1.1989</v>
       </c>
       <c r="J21" t="n">
-        <v>2.7814</v>
+        <v>-1.1641</v>
       </c>
       <c r="K21" t="n">
-        <v>3.6477</v>
+        <v>0.0973</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8662</v>
+        <v>-1.2613</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0549</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4673</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5222</v>
+        <v>0.0624</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.4932</v>
+        <v>-0.2055</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.3425</v>
+        <v>-1.0274</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8493</v>
+        <v>0.8219</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0003</v>
+        <v>0.6922</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4214</v>
+        <v>0.0872</v>
       </c>
       <c r="U21" t="n">
-        <v>0.421</v>
+        <v>0.605</v>
       </c>
       <c r="V21" t="n">
-        <v>1.637</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1781</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.4589</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>A. LINDQVIST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,58 +2214,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0105</v>
+        <v>-0.0726</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1043</v>
+        <v>-0.0682</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0937</v>
+        <v>-0.0044</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4973</v>
+        <v>0.0375</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7016</v>
+        <v>-0.0332</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1989</v>
+        <v>0.0707</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1641</v>
+        <v>0.0589</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0973</v>
+        <v>0.0195</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2613</v>
+        <v>0.0395</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6667999999999999</v>
+        <v>-0.0214</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6042999999999999</v>
+        <v>-0.0526</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0624</v>
+        <v>0.0312</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2055</v>
+        <v>0.2055</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0274</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8219</v>
+        <v>0.2055</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6922</v>
+        <v>-0.3156</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0872</v>
+        <v>-0.1271</v>
       </c>
       <c r="U22" t="n">
-        <v>0.605</v>
+        <v>-0.1885</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. LINDQVIST</t>
+          <t>A. HARO VAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,58 +2297,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0726</v>
+        <v>-0.4749</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0682</v>
+        <v>-1.5927</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0044</v>
+        <v>1.1179</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0375</v>
+        <v>-0.6068</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0332</v>
+        <v>-1.42</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0707</v>
+        <v>0.8132</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0589</v>
+        <v>-0.0582</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0195</v>
+        <v>-1.283</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0395</v>
+        <v>1.2247</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0214</v>
+        <v>-0.5486</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0526</v>
+        <v>-0.137</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0312</v>
+        <v>-0.4116</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2055</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.2329</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2055</v>
+        <v>1.2329</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3156</v>
+        <v>0.1319</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1271</v>
+        <v>-0.3016</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1885</v>
+        <v>0.4336</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. HARO VAL</t>
+          <t>P. FERNANDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,58 +2380,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4749</v>
+        <v>-0.5281</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5927</v>
+        <v>-0.1237</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1179</v>
+        <v>-0.4044</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6068</v>
+        <v>-0.3189</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.42</v>
+        <v>0.0756</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8132</v>
+        <v>-0.3945</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0582</v>
+        <v>0.0389</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.283</v>
+        <v>0.0389</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2247</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5486</v>
+        <v>-0.3578</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.137</v>
+        <v>0.0367</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4116</v>
+        <v>-0.3945</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-0.2055</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.2329</v>
+        <v>-0.2055</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2329</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1319</v>
+        <v>-0.0037</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3016</v>
+        <v>0.0429</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4336</v>
+        <v>-0.0466</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ CARBALLO</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,67 +2463,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5281</v>
+        <v>-1.2217</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1237</v>
+        <v>-2.1297</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4044</v>
+        <v>0.908</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3189</v>
+        <v>-0.0488</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0756</v>
+        <v>-0.2608</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3945</v>
+        <v>0.212</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0389</v>
+        <v>0.1573</v>
       </c>
       <c r="K25" t="n">
         <v>0.0389</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.1184</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3578</v>
+        <v>-0.2061</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0367</v>
+        <v>-0.2997</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3945</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.2055</v>
+        <v>-1.8493</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.2055</v>
+        <v>-2.0548</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>0.2055</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0037</v>
+        <v>-0.0222</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0429</v>
+        <v>-0.2321</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0466</v>
+        <v>0.21</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.6986</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.6986</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2546,152 +2546,69 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.2217</v>
+        <v>18.1312</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.1297</v>
+        <v>1.422500000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.908</v>
+        <v>16.7088</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0488</v>
+        <v>14.1421</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2608</v>
+        <v>1.682100000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.212</v>
+        <v>12.4599</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1573</v>
+        <v>15.7896</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0389</v>
+        <v>4.025</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1184</v>
+        <v>11.7647</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2061</v>
+        <v>-1.6476</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2997</v>
+        <v>-2.3428</v>
       </c>
       <c r="O26" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.6952999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.8493</v>
+        <v>-7.191799999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.0548</v>
+        <v>-21.5755</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2055</v>
+        <v>14.3836</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0222</v>
+        <v>3.5439</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2321</v>
+        <v>-1.1684</v>
       </c>
       <c r="U26" t="n">
-        <v>0.21</v>
+        <v>4.7123</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6986</v>
+        <v>7.6369</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>8.3766</v>
       </c>
       <c r="X26" t="n">
-        <v>0.6986</v>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>play_by_play_2536318_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>CLASS BASQUET SANT ANTONI</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>18.1312</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1.422500000000001</v>
-      </c>
-      <c r="F27" t="n">
-        <v>16.7088</v>
-      </c>
-      <c r="G27" t="n">
-        <v>14.1421</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.682100000000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>12.4599</v>
-      </c>
-      <c r="J27" t="n">
-        <v>15.7896</v>
-      </c>
-      <c r="K27" t="n">
-        <v>4.025</v>
-      </c>
-      <c r="L27" t="n">
-        <v>11.7647</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-1.6476</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-2.3428</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0.6952999999999999</v>
-      </c>
-      <c r="P27" t="n">
-        <v>-7.191799999999999</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-21.5755</v>
-      </c>
-      <c r="R27" t="n">
-        <v>14.3836</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.5439</v>
-      </c>
-      <c r="T27" t="n">
-        <v>-1.1684</v>
-      </c>
-      <c r="U27" t="n">
-        <v>4.7123</v>
-      </c>
-      <c r="V27" t="n">
-        <v>7.6369</v>
-      </c>
-      <c r="W27" t="n">
-        <v>8.3766</v>
-      </c>
-      <c r="X27" t="n">
         <v>-0.7396999999999997</v>
       </c>
-      <c r="Y27" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
